--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/30,07,26 ПОКОМ КИ/дв 30,07,26 млрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/30,07,26 ПОКОМ КИ/дв 30,07,26 млрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\30,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F988F179-74B2-4E11-B106-3620EA0580AC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42FFCBE9-8E17-495F-A5EA-338E8F5F5FF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,15 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AL$132</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -708,7 +700,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -722,9 +714,7 @@
     <xf numFmtId="2" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
@@ -746,8 +736,11 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sheet"/>
     </sheetNames>
@@ -1095,10 +1088,10 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="17">
+      <c r="V1" s="15">
         <v>2.2999999999999998</v>
       </c>
-      <c r="W1" s="17">
+      <c r="W1" s="15">
         <v>0.05</v>
       </c>
       <c r="X1" s="1"/>
@@ -1593,7 +1586,7 @@
       <c r="W6" s="5">
         <v>220</v>
       </c>
-      <c r="X6" s="14"/>
+      <c r="X6" s="1"/>
       <c r="Y6" s="1">
         <f>(F6+O6+P6+Q6+R6+S6+W6)/T6</f>
         <v>12.94420990512506</v>
@@ -1712,7 +1705,7 @@
         <f>U7+$W$1*T7</f>
         <v>687.99371000000031</v>
       </c>
-      <c r="X7" s="14"/>
+      <c r="X7" s="1"/>
       <c r="Y7" s="1">
         <f t="shared" ref="Y7:Y70" si="6">(F7+O7+P7+Q7+R7+S7+W7)/T7</f>
         <v>12.05</v>
@@ -1828,7 +1821,7 @@
         <f t="shared" ref="W8:W70" si="8">U8</f>
         <v>0</v>
       </c>
-      <c r="X8" s="14"/>
+      <c r="X8" s="1"/>
       <c r="Y8" s="1">
         <f t="shared" si="6"/>
         <v>12.505699599518458</v>
@@ -1940,7 +1933,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X9" s="14"/>
+      <c r="X9" s="1"/>
       <c r="Y9" s="1">
         <f t="shared" si="6"/>
         <v>35.200000000000003</v>
@@ -2059,7 +2052,7 @@
         <f t="shared" ref="W10:W11" si="9">U10+$W$1*T10</f>
         <v>238.42</v>
       </c>
-      <c r="X10" s="14"/>
+      <c r="X10" s="1"/>
       <c r="Y10" s="1">
         <f t="shared" si="6"/>
         <v>12.049999999999999</v>
@@ -2174,7 +2167,7 @@
         <f t="shared" si="9"/>
         <v>534.29999999999995</v>
       </c>
-      <c r="X11" s="14"/>
+      <c r="X11" s="1"/>
       <c r="Y11" s="1">
         <f t="shared" si="6"/>
         <v>12.05</v>
@@ -2276,7 +2269,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X12" s="15"/>
+      <c r="X12" s="9"/>
       <c r="Y12" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -2395,7 +2388,7 @@
         <f t="shared" si="8"/>
         <v>76.999999999999943</v>
       </c>
-      <c r="X13" s="14"/>
+      <c r="X13" s="1"/>
       <c r="Y13" s="1">
         <f t="shared" si="6"/>
         <v>11.999999999999998</v>
@@ -2512,7 +2505,7 @@
         <f t="shared" si="8"/>
         <v>111.80000000000001</v>
       </c>
-      <c r="X14" s="14"/>
+      <c r="X14" s="1"/>
       <c r="Y14" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -2629,7 +2622,7 @@
         <f>U15+$W$1*T15</f>
         <v>349.93367999999998</v>
       </c>
-      <c r="X15" s="14"/>
+      <c r="X15" s="1"/>
       <c r="Y15" s="1">
         <f t="shared" si="6"/>
         <v>12.049999999999999</v>
@@ -2745,7 +2738,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X16" s="14"/>
+      <c r="X16" s="1"/>
       <c r="Y16" s="1">
         <f t="shared" si="6"/>
         <v>13.963192769394349</v>
@@ -2862,7 +2855,7 @@
         <f t="shared" si="8"/>
         <v>23.791199999999911</v>
       </c>
-      <c r="X17" s="14"/>
+      <c r="X17" s="1"/>
       <c r="Y17" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -2979,7 +2972,7 @@
         <f t="shared" si="8"/>
         <v>35.797599999999981</v>
       </c>
-      <c r="X18" s="14"/>
+      <c r="X18" s="1"/>
       <c r="Y18" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3093,7 +3086,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X19" s="14"/>
+      <c r="X19" s="1"/>
       <c r="Y19" s="1">
         <f t="shared" si="6"/>
         <v>14.968409732490926</v>
@@ -3210,7 +3203,7 @@
         <f>U20+$W$1*T20</f>
         <v>257.59659000000033</v>
       </c>
-      <c r="X20" s="14"/>
+      <c r="X20" s="1"/>
       <c r="Y20" s="1">
         <f t="shared" si="6"/>
         <v>12.05</v>
@@ -3327,7 +3320,7 @@
         <f t="shared" si="8"/>
         <v>112.0868</v>
       </c>
-      <c r="X21" s="14"/>
+      <c r="X21" s="1"/>
       <c r="Y21" s="1">
         <f t="shared" si="6"/>
         <v>11.999999999999998</v>
@@ -3444,7 +3437,7 @@
         <f t="shared" si="8"/>
         <v>32.934599999999989</v>
       </c>
-      <c r="X22" s="14"/>
+      <c r="X22" s="1"/>
       <c r="Y22" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3561,7 +3554,7 @@
         <f t="shared" si="8"/>
         <v>15.446399999999999</v>
       </c>
-      <c r="X23" s="14"/>
+      <c r="X23" s="1"/>
       <c r="Y23" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -3678,7 +3671,7 @@
         <f t="shared" si="8"/>
         <v>207.77400000000011</v>
       </c>
-      <c r="X24" s="14"/>
+      <c r="X24" s="1"/>
       <c r="Y24" s="1">
         <f t="shared" si="6"/>
         <v>12.000000000000002</v>
@@ -3792,7 +3785,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X25" s="15"/>
+      <c r="X25" s="9"/>
       <c r="Y25" s="1">
         <f t="shared" si="6"/>
         <v>0.84086082849988908</v>
@@ -3894,7 +3887,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X26" s="15"/>
+      <c r="X26" s="9"/>
       <c r="Y26" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4013,7 +4006,7 @@
         <f t="shared" si="8"/>
         <v>311.05499999999984</v>
       </c>
-      <c r="X27" s="14"/>
+      <c r="X27" s="1"/>
       <c r="Y27" s="1">
         <f t="shared" si="6"/>
         <v>9.9999999999999982</v>
@@ -4132,7 +4125,7 @@
         <f t="shared" si="8"/>
         <v>517.44756000000007</v>
       </c>
-      <c r="X28" s="14"/>
+      <c r="X28" s="1"/>
       <c r="Y28" s="1">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -4244,7 +4237,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X29" s="14"/>
+      <c r="X29" s="1"/>
       <c r="Y29" s="1">
         <f t="shared" si="6"/>
         <v>-123.98241749309081</v>
@@ -4364,7 +4357,7 @@
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="X30" s="14"/>
+      <c r="X30" s="1"/>
       <c r="Y30" s="1">
         <f t="shared" si="6"/>
         <v>739.82315206893986</v>
@@ -4476,7 +4469,7 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="X31" s="14"/>
+      <c r="X31" s="1"/>
       <c r="Y31" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4586,7 +4579,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X32" s="14"/>
+      <c r="X32" s="1"/>
       <c r="Y32" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -4703,7 +4696,7 @@
         <f t="shared" si="8"/>
         <v>168.1884</v>
       </c>
-      <c r="X33" s="14"/>
+      <c r="X33" s="1"/>
       <c r="Y33" s="1">
         <f t="shared" si="6"/>
         <v>10</v>
@@ -4817,7 +4810,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X34" s="15"/>
+      <c r="X34" s="9"/>
       <c r="Y34" s="1">
         <f t="shared" si="6"/>
         <v>4.5362090128002803</v>
@@ -4934,7 +4927,7 @@
         <f t="shared" si="8"/>
         <v>101.79559999999998</v>
       </c>
-      <c r="X35" s="14"/>
+      <c r="X35" s="1"/>
       <c r="Y35" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -5053,7 +5046,7 @@
         <f>U36+$W$1*T36</f>
         <v>331.92200000000003</v>
       </c>
-      <c r="X36" s="14"/>
+      <c r="X36" s="1"/>
       <c r="Y36" s="1">
         <f t="shared" si="6"/>
         <v>12.05</v>
@@ -5170,7 +5163,7 @@
         <f t="shared" si="8"/>
         <v>42.799999999999955</v>
       </c>
-      <c r="X37" s="14"/>
+      <c r="X37" s="1"/>
       <c r="Y37" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -5284,7 +5277,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X38" s="14"/>
+      <c r="X38" s="1"/>
       <c r="Y38" s="1">
         <f t="shared" si="6"/>
         <v>19.416842105263147</v>
@@ -5398,7 +5391,7 @@
         <f t="shared" si="8"/>
         <v>30</v>
       </c>
-      <c r="X39" s="14"/>
+      <c r="X39" s="1"/>
       <c r="Y39" s="1">
         <f t="shared" si="6"/>
         <v>22.866666666666664</v>
@@ -5514,7 +5507,7 @@
       <c r="W40" s="5">
         <v>70</v>
       </c>
-      <c r="X40" s="14">
+      <c r="X40" s="1">
         <v>80</v>
       </c>
       <c r="Y40" s="1">
@@ -5632,7 +5625,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X41" s="14"/>
+      <c r="X41" s="1"/>
       <c r="Y41" s="1">
         <f t="shared" si="6"/>
         <v>14.148837209302322</v>
@@ -5748,7 +5741,7 @@
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="X42" s="14"/>
+      <c r="X42" s="1"/>
       <c r="Y42" s="1">
         <f t="shared" si="6"/>
         <v>66.285714285714292</v>
@@ -5865,7 +5858,7 @@
         <f t="shared" si="8"/>
         <v>102.15480000000002</v>
       </c>
-      <c r="X43" s="14"/>
+      <c r="X43" s="1"/>
       <c r="Y43" s="1">
         <f t="shared" si="6"/>
         <v>11.999999999999998</v>
@@ -5977,7 +5970,7 @@
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="X44" s="14"/>
+      <c r="X44" s="1"/>
       <c r="Y44" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -6089,7 +6082,7 @@
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="X45" s="14"/>
+      <c r="X45" s="1"/>
       <c r="Y45" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -6203,7 +6196,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X46" s="15"/>
+      <c r="X46" s="9"/>
       <c r="Y46" s="1">
         <f t="shared" si="6"/>
         <v>0.40138882745809185</v>
@@ -6320,7 +6313,7 @@
         <f t="shared" si="8"/>
         <v>38.09920000000001</v>
       </c>
-      <c r="X47" s="14"/>
+      <c r="X47" s="1"/>
       <c r="Y47" s="1">
         <f t="shared" si="6"/>
         <v>12.000000000000002</v>
@@ -6438,7 +6431,7 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="X48" s="14"/>
+      <c r="X48" s="1"/>
       <c r="Y48" s="1">
         <f t="shared" si="6"/>
         <v>15.760588235294115</v>
@@ -6558,7 +6551,7 @@
         <f t="shared" si="8"/>
         <v>150</v>
       </c>
-      <c r="X49" s="14"/>
+      <c r="X49" s="1"/>
       <c r="Y49" s="1">
         <f t="shared" si="6"/>
         <v>170.125</v>
@@ -6675,7 +6668,7 @@
         <f t="shared" si="8"/>
         <v>100.05320000000002</v>
       </c>
-      <c r="X50" s="14"/>
+      <c r="X50" s="1"/>
       <c r="Y50" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -6789,7 +6782,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X51" s="14"/>
+      <c r="X51" s="1"/>
       <c r="Y51" s="1">
         <f t="shared" si="6"/>
         <v>12.694797183932625</v>
@@ -6903,7 +6896,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X52" s="14"/>
+      <c r="X52" s="1"/>
       <c r="Y52" s="1">
         <f t="shared" si="6"/>
         <v>28.646444212721587</v>
@@ -7020,7 +7013,7 @@
         <f t="shared" si="8"/>
         <v>30.399999999999949</v>
       </c>
-      <c r="X53" s="14"/>
+      <c r="X53" s="1"/>
       <c r="Y53" s="1">
         <f t="shared" si="6"/>
         <v>11.999999999999998</v>
@@ -7136,7 +7129,7 @@
       <c r="W54" s="5">
         <v>200</v>
       </c>
-      <c r="X54" s="14"/>
+      <c r="X54" s="1"/>
       <c r="Y54" s="1">
         <f t="shared" si="6"/>
         <v>12.85823754789272</v>
@@ -7253,7 +7246,7 @@
         <f t="shared" si="8"/>
         <v>43.400000000000034</v>
       </c>
-      <c r="X55" s="14"/>
+      <c r="X55" s="1"/>
       <c r="Y55" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -7367,7 +7360,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X56" s="14"/>
+      <c r="X56" s="1"/>
       <c r="Y56" s="1">
         <f t="shared" si="6"/>
         <v>15.416666666666675</v>
@@ -7484,7 +7477,7 @@
         <f t="shared" si="8"/>
         <v>127.80300000000004</v>
       </c>
-      <c r="X57" s="14"/>
+      <c r="X57" s="1"/>
       <c r="Y57" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -7601,7 +7594,7 @@
         <f t="shared" si="8"/>
         <v>290.99999999999994</v>
       </c>
-      <c r="X58" s="14"/>
+      <c r="X58" s="1"/>
       <c r="Y58" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -7718,7 +7711,7 @@
         <f t="shared" si="8"/>
         <v>102.64599999999997</v>
       </c>
-      <c r="X59" s="14"/>
+      <c r="X59" s="1"/>
       <c r="Y59" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -7835,7 +7828,7 @@
         <f t="shared" si="8"/>
         <v>50.938400000000001</v>
       </c>
-      <c r="X60" s="14"/>
+      <c r="X60" s="1"/>
       <c r="Y60" s="1">
         <f t="shared" si="6"/>
         <v>11.999999999999998</v>
@@ -7952,7 +7945,7 @@
         <f t="shared" si="8"/>
         <v>69.800000000000068</v>
       </c>
-      <c r="X61" s="14"/>
+      <c r="X61" s="1"/>
       <c r="Y61" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -8069,7 +8062,7 @@
         <f t="shared" si="8"/>
         <v>21</v>
       </c>
-      <c r="X62" s="14"/>
+      <c r="X62" s="1"/>
       <c r="Y62" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -8184,7 +8177,7 @@
       <c r="W63" s="5">
         <v>60</v>
       </c>
-      <c r="X63" s="14">
+      <c r="X63" s="1">
         <v>80</v>
       </c>
       <c r="Y63" s="1">
@@ -8302,7 +8295,7 @@
       <c r="W64" s="5">
         <v>80</v>
       </c>
-      <c r="X64" s="14">
+      <c r="X64" s="1">
         <v>80</v>
       </c>
       <c r="Y64" s="1">
@@ -8418,7 +8411,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="X65" s="14"/>
+      <c r="X65" s="1"/>
       <c r="Y65" s="1">
         <f t="shared" si="6"/>
         <v>480.1999999999997</v>
@@ -8538,7 +8531,7 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="X66" s="14"/>
+      <c r="X66" s="1"/>
       <c r="Y66" s="1" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
@@ -8655,7 +8648,7 @@
         <f t="shared" si="8"/>
         <v>113.04379999999993</v>
       </c>
-      <c r="X67" s="14"/>
+      <c r="X67" s="1"/>
       <c r="Y67" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -8772,7 +8765,7 @@
         <f t="shared" si="8"/>
         <v>192.20548000000005</v>
       </c>
-      <c r="X68" s="14"/>
+      <c r="X68" s="1"/>
       <c r="Y68" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -8889,7 +8882,7 @@
         <f>U69+$W$1*T69</f>
         <v>264.80350999999979</v>
       </c>
-      <c r="X69" s="14"/>
+      <c r="X69" s="1"/>
       <c r="Y69" s="1">
         <f t="shared" si="6"/>
         <v>12.049999999999999</v>
@@ -9006,7 +8999,7 @@
         <f t="shared" si="8"/>
         <v>101.97559999999987</v>
       </c>
-      <c r="X70" s="14"/>
+      <c r="X70" s="1"/>
       <c r="Y70" s="1">
         <f t="shared" si="6"/>
         <v>12</v>
@@ -9120,7 +9113,7 @@
         <f t="shared" ref="W71:W132" si="16">U71</f>
         <v>0</v>
       </c>
-      <c r="X71" s="14"/>
+      <c r="X71" s="1"/>
       <c r="Y71" s="1">
         <f t="shared" ref="Y71:Y132" si="17">(F71+O71+P71+Q71+R71+S71+W71)/T71</f>
         <v>78.75</v>
@@ -9236,7 +9229,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X72" s="14"/>
+      <c r="X72" s="1"/>
       <c r="Y72" s="1">
         <f t="shared" si="17"/>
         <v>18.803238412251339</v>
@@ -9338,7 +9331,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X73" s="15"/>
+      <c r="X73" s="9"/>
       <c r="Y73" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -9454,7 +9447,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X74" s="14"/>
+      <c r="X74" s="1"/>
       <c r="Y74" s="1">
         <f t="shared" si="17"/>
         <v>27.439024390243905</v>
@@ -9571,7 +9564,7 @@
         <f t="shared" si="16"/>
         <v>45.000000000000057</v>
       </c>
-      <c r="X75" s="14"/>
+      <c r="X75" s="1"/>
       <c r="Y75" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -9688,7 +9681,7 @@
         <f t="shared" si="16"/>
         <v>159</v>
       </c>
-      <c r="X76" s="14"/>
+      <c r="X76" s="1"/>
       <c r="Y76" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -9805,7 +9798,7 @@
         <f t="shared" si="16"/>
         <v>89.199999999999989</v>
       </c>
-      <c r="X77" s="14"/>
+      <c r="X77" s="1"/>
       <c r="Y77" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -9922,7 +9915,7 @@
         <f t="shared" si="16"/>
         <v>37.399999999999977</v>
       </c>
-      <c r="X78" s="14"/>
+      <c r="X78" s="1"/>
       <c r="Y78" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -10024,7 +10017,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X79" s="15"/>
+      <c r="X79" s="9"/>
       <c r="Y79" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -10140,7 +10133,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X80" s="14"/>
+      <c r="X80" s="1"/>
       <c r="Y80" s="1">
         <f t="shared" si="17"/>
         <v>12.195121951219512</v>
@@ -10252,7 +10245,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X81" s="14"/>
+      <c r="X81" s="1"/>
       <c r="Y81" s="1">
         <f t="shared" si="17"/>
         <v>48.906976744186053</v>
@@ -10369,7 +10362,7 @@
         <f t="shared" si="16"/>
         <v>44.599999999999994</v>
       </c>
-      <c r="X82" s="14"/>
+      <c r="X82" s="1"/>
       <c r="Y82" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -10484,7 +10477,7 @@
         <f t="shared" si="16"/>
         <v>74</v>
       </c>
-      <c r="X83" s="14"/>
+      <c r="X83" s="1"/>
       <c r="Y83" s="1">
         <f t="shared" si="17"/>
         <v>11</v>
@@ -10586,7 +10579,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X84" s="15"/>
+      <c r="X84" s="9"/>
       <c r="Y84" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -10690,7 +10683,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X85" s="15"/>
+      <c r="X85" s="9"/>
       <c r="Y85" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -10804,7 +10797,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X86" s="15"/>
+      <c r="X86" s="9"/>
       <c r="Y86" s="1">
         <f t="shared" si="17"/>
         <v>0.58139534883720934</v>
@@ -10916,7 +10909,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X87" s="14"/>
+      <c r="X87" s="1"/>
       <c r="Y87" s="1">
         <f t="shared" si="17"/>
         <v>13.574160772985357</v>
@@ -11033,7 +11026,7 @@
         <f t="shared" si="16"/>
         <v>73.187999999999931</v>
       </c>
-      <c r="X88" s="14"/>
+      <c r="X88" s="1"/>
       <c r="Y88" s="1">
         <f t="shared" si="17"/>
         <v>11.999999999999998</v>
@@ -11135,7 +11128,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X89" s="15"/>
+      <c r="X89" s="9"/>
       <c r="Y89" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -11257,7 +11250,7 @@
         <f>U90+$W$1*T90</f>
         <v>1353.0125219199977</v>
       </c>
-      <c r="X90" s="14"/>
+      <c r="X90" s="1"/>
       <c r="Y90" s="1">
         <f t="shared" si="17"/>
         <v>12.05</v>
@@ -11315,7 +11308,7 @@
       <c r="AX90" s="1"/>
     </row>
     <row r="91" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A91" s="16" t="s">
+      <c r="A91" s="14" t="s">
         <v>130</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -11379,7 +11372,7 @@
         <f t="shared" si="16"/>
         <v>929.15559999999914</v>
       </c>
-      <c r="X91" s="14"/>
+      <c r="X91" s="1"/>
       <c r="Y91" s="1">
         <f t="shared" si="17"/>
         <v>11.999999999999998</v>
@@ -11437,7 +11430,7 @@
       <c r="AX91" s="1"/>
     </row>
     <row r="92" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="14" t="s">
         <v>131</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -11498,7 +11491,7 @@
         <f t="shared" si="16"/>
         <v>1430.9216000000006</v>
       </c>
-      <c r="X92" s="14"/>
+      <c r="X92" s="1"/>
       <c r="Y92" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -11600,7 +11593,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X93" s="15"/>
+      <c r="X93" s="9"/>
       <c r="Y93" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -11718,7 +11711,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X94" s="14"/>
+      <c r="X94" s="1"/>
       <c r="Y94" s="1">
         <f t="shared" si="17"/>
         <v>14.331428571428571</v>
@@ -11820,7 +11813,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X95" s="15"/>
+      <c r="X95" s="9"/>
       <c r="Y95" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -11936,7 +11929,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X96" s="14"/>
+      <c r="X96" s="1"/>
       <c r="Y96" s="1">
         <f t="shared" si="17"/>
         <v>17.553191489361701</v>
@@ -12053,7 +12046,7 @@
         <f t="shared" si="16"/>
         <v>59.2</v>
       </c>
-      <c r="X97" s="14"/>
+      <c r="X97" s="1"/>
       <c r="Y97" s="1">
         <f t="shared" si="17"/>
         <v>11</v>
@@ -12167,7 +12160,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X98" s="14"/>
+      <c r="X98" s="1"/>
       <c r="Y98" s="1">
         <f t="shared" si="17"/>
         <v>21.800000000000004</v>
@@ -12279,7 +12272,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X99" s="15"/>
+      <c r="X99" s="9"/>
       <c r="Y99" s="1">
         <f t="shared" si="17"/>
         <v>2.3809523809523809</v>
@@ -12387,7 +12380,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X100" s="15"/>
+      <c r="X100" s="9"/>
       <c r="Y100" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -12491,7 +12484,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X101" s="15"/>
+      <c r="X101" s="9"/>
       <c r="Y101" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -12603,7 +12596,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X102" s="15"/>
+      <c r="X102" s="9"/>
       <c r="Y102" s="1">
         <f t="shared" si="17"/>
         <v>-5</v>
@@ -12707,7 +12700,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X103" s="15"/>
+      <c r="X103" s="9"/>
       <c r="Y103" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -12811,7 +12804,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X104" s="15"/>
+      <c r="X104" s="9"/>
       <c r="Y104" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -12930,7 +12923,7 @@
         <f t="shared" si="16"/>
         <v>27.199999999999989</v>
       </c>
-      <c r="X105" s="14"/>
+      <c r="X105" s="1"/>
       <c r="Y105" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -13044,7 +13037,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X106" s="14"/>
+      <c r="X106" s="1"/>
       <c r="Y106" s="1">
         <f t="shared" si="17"/>
         <v>15.425531914893616</v>
@@ -13148,7 +13141,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X107" s="15"/>
+      <c r="X107" s="9"/>
       <c r="Y107" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -13267,7 +13260,7 @@
         <f t="shared" si="16"/>
         <v>176.23179999999985</v>
       </c>
-      <c r="X108" s="14"/>
+      <c r="X108" s="1"/>
       <c r="Y108" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -13384,7 +13377,7 @@
         <f t="shared" si="16"/>
         <v>162.94699999999997</v>
       </c>
-      <c r="X109" s="14"/>
+      <c r="X109" s="1"/>
       <c r="Y109" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -13501,7 +13494,7 @@
         <f t="shared" si="16"/>
         <v>198.77567999999985</v>
       </c>
-      <c r="X110" s="14"/>
+      <c r="X110" s="1"/>
       <c r="Y110" s="1">
         <f t="shared" si="17"/>
         <v>12.000000000000002</v>
@@ -13603,7 +13596,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X111" s="15"/>
+      <c r="X111" s="9"/>
       <c r="Y111" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -13707,7 +13700,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X112" s="15"/>
+      <c r="X112" s="9"/>
       <c r="Y112" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -13826,7 +13819,7 @@
         <f t="shared" si="16"/>
         <v>266.20000000000005</v>
       </c>
-      <c r="X113" s="14"/>
+      <c r="X113" s="1"/>
       <c r="Y113" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -13943,7 +13936,7 @@
         <f t="shared" si="16"/>
         <v>144.80000000000007</v>
       </c>
-      <c r="X114" s="14"/>
+      <c r="X114" s="1"/>
       <c r="Y114" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -14060,7 +14053,7 @@
         <f t="shared" si="16"/>
         <v>140.60000000000002</v>
       </c>
-      <c r="X115" s="14"/>
+      <c r="X115" s="1"/>
       <c r="Y115" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -14162,7 +14155,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X116" s="15"/>
+      <c r="X116" s="9"/>
       <c r="Y116" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -14280,7 +14273,7 @@
         <f t="shared" si="16"/>
         <v>4</v>
       </c>
-      <c r="X117" s="14"/>
+      <c r="X117" s="1"/>
       <c r="Y117" s="1">
         <f t="shared" si="17"/>
         <v>12.192206024344303</v>
@@ -14394,7 +14387,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X118" s="14"/>
+      <c r="X118" s="1"/>
       <c r="Y118" s="1">
         <f t="shared" si="17"/>
         <v>18.090815111131089</v>
@@ -14496,7 +14489,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X119" s="15"/>
+      <c r="X119" s="9"/>
       <c r="Y119" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -14600,7 +14593,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X120" s="15"/>
+      <c r="X120" s="9"/>
       <c r="Y120" s="1" t="e">
         <f t="shared" si="17"/>
         <v>#DIV/0!</v>
@@ -14719,7 +14712,7 @@
         <f t="shared" si="16"/>
         <v>172.62720000000002</v>
       </c>
-      <c r="X121" s="14"/>
+      <c r="X121" s="1"/>
       <c r="Y121" s="1">
         <f t="shared" si="17"/>
         <v>11</v>
@@ -14836,7 +14829,7 @@
         <f t="shared" si="16"/>
         <v>12.416399999999882</v>
       </c>
-      <c r="X122" s="14"/>
+      <c r="X122" s="1"/>
       <c r="Y122" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -14950,7 +14943,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X123" s="14"/>
+      <c r="X123" s="1"/>
       <c r="Y123" s="1">
         <f t="shared" si="17"/>
         <v>36.883638036104401</v>
@@ -15008,7 +15001,7 @@
       <c r="AX123" s="1"/>
     </row>
     <row r="124" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A124" s="16" t="s">
+      <c r="A124" s="14" t="s">
         <v>166</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -15072,7 +15065,7 @@
         <f t="shared" si="16"/>
         <v>282.22840000000042</v>
       </c>
-      <c r="X124" s="14"/>
+      <c r="X124" s="1"/>
       <c r="Y124" s="1">
         <f t="shared" si="17"/>
         <v>12.000000000000002</v>
@@ -15192,7 +15185,7 @@
       <c r="W125" s="5">
         <v>330</v>
       </c>
-      <c r="X125" s="14"/>
+      <c r="X125" s="1"/>
       <c r="Y125" s="1">
         <f t="shared" si="17"/>
         <v>12.560439560439557</v>
@@ -15304,7 +15297,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X126" s="14"/>
+      <c r="X126" s="1"/>
       <c r="Y126" s="1">
         <f t="shared" si="17"/>
         <v>-298.00000000000011</v>
@@ -15423,7 +15416,7 @@
         <f t="shared" si="16"/>
         <v>4.7130000000000045</v>
       </c>
-      <c r="X127" s="14"/>
+      <c r="X127" s="1"/>
       <c r="Y127" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -15540,7 +15533,7 @@
         <f t="shared" si="16"/>
         <v>209.39999999999998</v>
       </c>
-      <c r="X128" s="14"/>
+      <c r="X128" s="1"/>
       <c r="Y128" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -15654,7 +15647,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X129" s="14"/>
+      <c r="X129" s="1"/>
       <c r="Y129" s="1">
         <f t="shared" si="17"/>
         <v>13.864406779661017</v>
@@ -15767,7 +15760,7 @@
         <f t="shared" si="16"/>
         <v>37.199999999999989</v>
       </c>
-      <c r="X130" s="14"/>
+      <c r="X130" s="1"/>
       <c r="Y130" s="1">
         <f t="shared" si="17"/>
         <v>12</v>
@@ -15879,7 +15872,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X131" s="14"/>
+      <c r="X131" s="1"/>
       <c r="Y131" s="1">
         <f t="shared" si="17"/>
         <v>45</v>
@@ -15991,7 +15984,7 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="X132" s="14"/>
+      <c r="X132" s="1"/>
       <c r="Y132" s="1">
         <f t="shared" si="17"/>
         <v>15.555555555555555</v>
